--- a/ProducaoIndustrial2026.xlsx
+++ b/ProducaoIndustrial2026.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wkuba\Projetos\analisador_producao\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45CBE926-C136-4E8D-B51E-008A887DF0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produção Diária" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -22,12 +28,6 @@
     <t>Time</t>
   </si>
   <si>
-    <t>Terminal MP35</t>
-  </si>
-  <si>
-    <t>Terminal MP30</t>
-  </si>
-  <si>
     <t>Ana Silva</t>
   </si>
   <si>
@@ -191,13 +191,19 @@
   </si>
   <si>
     <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>Terminal MP1</t>
+  </si>
+  <si>
+    <t>Terminal MP1S</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,13 +240,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -278,7 +292,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -312,6 +326,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -346,9 +361,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -521,11 +537,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X176"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -533,75 +555,75 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24">
-      <c r="A2" t="s">
-        <v>24</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -625,9 +647,9 @@
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -651,9 +673,9 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -677,9 +699,9 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -703,9 +725,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -729,9 +751,9 @@
         <v>488</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -755,9 +777,9 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -781,9 +803,9 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -807,9 +829,9 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -833,9 +855,9 @@
         <v>370</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -859,9 +881,9 @@
         <v>424</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -885,9 +907,9 @@
         <v>692</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -911,9 +933,9 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -937,9 +959,9 @@
         <v>784</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>4</v>
@@ -963,9 +985,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -989,9 +1011,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1015,9 +1037,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -1041,9 +1063,9 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>3</v>
@@ -1067,9 +1089,9 @@
         <v>248</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -1093,9 +1115,9 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -1119,9 +1141,9 @@
         <v>870</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -1145,9 +1167,9 @@
         <v>445</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -1171,9 +1193,9 @@
         <v>640</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -1197,9 +1219,9 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B25">
         <v>4</v>
@@ -1223,9 +1245,9 @@
         <v>729</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>5</v>
@@ -1249,9 +1271,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -1275,9 +1297,9 @@
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -1301,9 +1323,9 @@
         <v>559</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -1327,9 +1349,9 @@
         <v>490</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -1353,9 +1375,9 @@
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>5</v>
@@ -1379,9 +1401,9 @@
         <v>492</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -1405,9 +1427,9 @@
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -1431,9 +1453,9 @@
         <v>155</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B34">
         <v>3</v>
@@ -1457,9 +1479,9 @@
         <v>651</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B35">
         <v>4</v>
@@ -1483,9 +1505,9 @@
         <v>574</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B36">
         <v>5</v>
@@ -1509,9 +1531,9 @@
         <v>684</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -1535,9 +1557,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B38">
         <v>2</v>
@@ -1561,9 +1583,9 @@
         <v>433</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -1587,9 +1609,9 @@
         <v>595</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>4</v>
@@ -1613,9 +1635,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B41">
         <v>5</v>
@@ -1639,9 +1661,9 @@
         <v>167</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -1665,9 +1687,9 @@
         <v>251</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B43">
         <v>2</v>
@@ -1691,9 +1713,9 @@
         <v>225</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B44">
         <v>3</v>
@@ -1717,9 +1739,9 @@
         <v>545</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B45">
         <v>4</v>
@@ -1743,9 +1765,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B46">
         <v>5</v>
@@ -1769,9 +1791,9 @@
         <v>845</v>
       </c>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -1795,9 +1817,9 @@
         <v>496</v>
       </c>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B48">
         <v>2</v>
@@ -1821,9 +1843,9 @@
         <v>786</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B49">
         <v>3</v>
@@ -1847,9 +1869,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B50">
         <v>4</v>
@@ -1873,9 +1895,9 @@
         <v>192</v>
       </c>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B51">
         <v>5</v>
@@ -1899,9 +1921,9 @@
         <v>739</v>
       </c>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -1925,9 +1947,9 @@
         <v>191</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -1951,9 +1973,9 @@
         <v>370</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B54">
         <v>3</v>
@@ -1977,9 +1999,9 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B55">
         <v>4</v>
@@ -2003,9 +2025,9 @@
         <v>317</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B56">
         <v>5</v>
@@ -2029,9 +2051,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -2055,9 +2077,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -2081,9 +2103,9 @@
         <v>756</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B59">
         <v>3</v>
@@ -2107,9 +2129,9 @@
         <v>692</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B60">
         <v>4</v>
@@ -2133,9 +2155,9 @@
         <v>787</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B61">
         <v>5</v>
@@ -2159,9 +2181,9 @@
         <v>458</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -2185,9 +2207,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -2211,9 +2233,9 @@
         <v>353</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -2237,9 +2259,9 @@
         <v>305</v>
       </c>
     </row>
-    <row r="65" spans="1:24">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B65">
         <v>4</v>
@@ -2263,9 +2285,9 @@
         <v>163</v>
       </c>
     </row>
-    <row r="66" spans="1:24">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B66">
         <v>5</v>
@@ -2289,9 +2311,9 @@
         <v>264</v>
       </c>
     </row>
-    <row r="67" spans="1:24">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -2315,9 +2337,9 @@
         <v>248</v>
       </c>
     </row>
-    <row r="68" spans="1:24">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -2341,9 +2363,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="69" spans="1:24">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B69">
         <v>3</v>
@@ -2367,9 +2389,9 @@
         <v>211</v>
       </c>
     </row>
-    <row r="70" spans="1:24">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B70">
         <v>4</v>
@@ -2393,9 +2415,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="71" spans="1:24">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B71">
         <v>5</v>
@@ -2419,9 +2441,9 @@
         <v>787</v>
       </c>
     </row>
-    <row r="72" spans="1:24">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -2445,9 +2467,9 @@
         <v>275</v>
       </c>
     </row>
-    <row r="73" spans="1:24">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -2471,9 +2493,9 @@
         <v>277</v>
       </c>
     </row>
-    <row r="74" spans="1:24">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B74">
         <v>3</v>
@@ -2497,9 +2519,9 @@
         <v>877</v>
       </c>
     </row>
-    <row r="75" spans="1:24">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B75">
         <v>4</v>
@@ -2523,9 +2545,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:24">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B76">
         <v>5</v>
@@ -2549,9 +2571,9 @@
         <v>280</v>
       </c>
     </row>
-    <row r="77" spans="1:24">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -2575,9 +2597,9 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="78" spans="1:24">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -2601,9 +2623,9 @@
         <v>620</v>
       </c>
     </row>
-    <row r="79" spans="1:24">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B79">
         <v>3</v>
@@ -2627,9 +2649,9 @@
         <v>742</v>
       </c>
     </row>
-    <row r="80" spans="1:24">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B80">
         <v>4</v>
@@ -2653,9 +2675,9 @@
         <v>305</v>
       </c>
     </row>
-    <row r="81" spans="1:24">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B81">
         <v>5</v>
@@ -2679,9 +2701,9 @@
         <v>896</v>
       </c>
     </row>
-    <row r="82" spans="1:24">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -2705,9 +2727,9 @@
         <v>227</v>
       </c>
     </row>
-    <row r="83" spans="1:24">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -2731,9 +2753,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="84" spans="1:24">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B84">
         <v>3</v>
@@ -2757,9 +2779,9 @@
         <v>973</v>
       </c>
     </row>
-    <row r="85" spans="1:24">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B85">
         <v>4</v>
@@ -2783,9 +2805,9 @@
         <v>423</v>
       </c>
     </row>
-    <row r="86" spans="1:24">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B86">
         <v>5</v>
@@ -2809,9 +2831,9 @@
         <v>228</v>
       </c>
     </row>
-    <row r="87" spans="1:24">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -2835,9 +2857,9 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="88" spans="1:24">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -2861,9 +2883,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="89" spans="1:24">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B89">
         <v>3</v>
@@ -2887,9 +2909,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="90" spans="1:24">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B90">
         <v>4</v>
@@ -2913,9 +2935,9 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="91" spans="1:24">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B91">
         <v>5</v>
@@ -2939,9 +2961,9 @@
         <v>73</v>
       </c>
     </row>
-    <row r="92" spans="1:24">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -2965,9 +2987,9 @@
         <v>310</v>
       </c>
     </row>
-    <row r="93" spans="1:24">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -2991,9 +3013,9 @@
         <v>985</v>
       </c>
     </row>
-    <row r="94" spans="1:24">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -3017,9 +3039,9 @@
         <v>682</v>
       </c>
     </row>
-    <row r="95" spans="1:24">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B95">
         <v>4</v>
@@ -3043,9 +3065,9 @@
         <v>294</v>
       </c>
     </row>
-    <row r="96" spans="1:24">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B96">
         <v>5</v>
@@ -3069,9 +3091,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="97" spans="1:24">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -3095,9 +3117,9 @@
         <v>228</v>
       </c>
     </row>
-    <row r="98" spans="1:24">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -3121,9 +3143,9 @@
         <v>400</v>
       </c>
     </row>
-    <row r="99" spans="1:24">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B99">
         <v>3</v>
@@ -3147,9 +3169,9 @@
         <v>960</v>
       </c>
     </row>
-    <row r="100" spans="1:24">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B100">
         <v>4</v>
@@ -3173,9 +3195,9 @@
         <v>891</v>
       </c>
     </row>
-    <row r="101" spans="1:24">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B101">
         <v>5</v>
@@ -3199,9 +3221,9 @@
         <v>593</v>
       </c>
     </row>
-    <row r="102" spans="1:24">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -3225,9 +3247,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="103" spans="1:24">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B103">
         <v>2</v>
@@ -3251,9 +3273,9 @@
         <v>428</v>
       </c>
     </row>
-    <row r="104" spans="1:24">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B104">
         <v>3</v>
@@ -3277,9 +3299,9 @@
         <v>505</v>
       </c>
     </row>
-    <row r="105" spans="1:24">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B105">
         <v>4</v>
@@ -3303,9 +3325,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="106" spans="1:24">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B106">
         <v>5</v>
@@ -3329,9 +3351,9 @@
         <v>311</v>
       </c>
     </row>
-    <row r="107" spans="1:24">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -3355,9 +3377,9 @@
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:24">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B108">
         <v>2</v>
@@ -3381,9 +3403,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="109" spans="1:24">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -3407,9 +3429,9 @@
         <v>213</v>
       </c>
     </row>
-    <row r="110" spans="1:24">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B110">
         <v>4</v>
@@ -3433,9 +3455,9 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="111" spans="1:24">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B111">
         <v>5</v>
@@ -3459,9 +3481,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:24">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -3485,9 +3507,9 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="113" spans="1:24">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B113">
         <v>2</v>
@@ -3511,9 +3533,9 @@
         <v>181</v>
       </c>
     </row>
-    <row r="114" spans="1:24">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B114">
         <v>3</v>
@@ -3537,9 +3559,9 @@
         <v>712</v>
       </c>
     </row>
-    <row r="115" spans="1:24">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B115">
         <v>4</v>
@@ -3563,9 +3585,9 @@
         <v>386</v>
       </c>
     </row>
-    <row r="116" spans="1:24">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B116">
         <v>5</v>
@@ -3589,9 +3611,9 @@
         <v>476</v>
       </c>
     </row>
-    <row r="117" spans="1:24">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -3615,9 +3637,9 @@
         <v>146</v>
       </c>
     </row>
-    <row r="118" spans="1:24">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B118">
         <v>2</v>
@@ -3641,9 +3663,9 @@
         <v>734</v>
       </c>
     </row>
-    <row r="119" spans="1:24">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B119">
         <v>3</v>
@@ -3667,9 +3689,9 @@
         <v>435</v>
       </c>
     </row>
-    <row r="120" spans="1:24">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B120">
         <v>4</v>
@@ -3693,9 +3715,9 @@
         <v>583</v>
       </c>
     </row>
-    <row r="121" spans="1:24">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B121">
         <v>5</v>
@@ -3719,9 +3741,9 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="122" spans="1:24">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -3745,9 +3767,9 @@
         <v>714</v>
       </c>
     </row>
-    <row r="123" spans="1:24">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B123">
         <v>2</v>
@@ -3771,9 +3793,9 @@
         <v>498</v>
       </c>
     </row>
-    <row r="124" spans="1:24">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B124">
         <v>3</v>
@@ -3797,9 +3819,9 @@
         <v>669</v>
       </c>
     </row>
-    <row r="125" spans="1:24">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B125">
         <v>4</v>
@@ -3823,9 +3845,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="126" spans="1:24">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B126">
         <v>5</v>
@@ -3849,9 +3871,9 @@
         <v>217</v>
       </c>
     </row>
-    <row r="127" spans="1:24">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -3875,9 +3897,9 @@
         <v>724</v>
       </c>
     </row>
-    <row r="128" spans="1:24">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B128">
         <v>2</v>
@@ -3901,9 +3923,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="129" spans="1:24">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B129">
         <v>3</v>
@@ -3927,9 +3949,9 @@
         <v>537</v>
       </c>
     </row>
-    <row r="130" spans="1:24">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B130">
         <v>4</v>
@@ -3953,9 +3975,9 @@
         <v>354</v>
       </c>
     </row>
-    <row r="131" spans="1:24">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B131">
         <v>5</v>
@@ -3979,9 +4001,9 @@
         <v>244</v>
       </c>
     </row>
-    <row r="132" spans="1:24">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -4005,9 +4027,9 @@
         <v>307</v>
       </c>
     </row>
-    <row r="133" spans="1:24">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B133">
         <v>2</v>
@@ -4031,9 +4053,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="134" spans="1:24">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B134">
         <v>3</v>
@@ -4057,9 +4079,9 @@
         <v>105</v>
       </c>
     </row>
-    <row r="135" spans="1:24">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B135">
         <v>4</v>
@@ -4083,9 +4105,9 @@
         <v>833</v>
       </c>
     </row>
-    <row r="136" spans="1:24">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B136">
         <v>5</v>
@@ -4109,9 +4131,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="137" spans="1:24">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -4135,9 +4157,9 @@
         <v>727</v>
       </c>
     </row>
-    <row r="138" spans="1:24">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B138">
         <v>2</v>
@@ -4161,9 +4183,9 @@
         <v>601</v>
       </c>
     </row>
-    <row r="139" spans="1:24">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B139">
         <v>3</v>
@@ -4187,9 +4209,9 @@
         <v>528</v>
       </c>
     </row>
-    <row r="140" spans="1:24">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B140">
         <v>4</v>
@@ -4213,9 +4235,9 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="141" spans="1:24">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B141">
         <v>5</v>
@@ -4239,9 +4261,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="142" spans="1:24">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -4265,9 +4287,9 @@
         <v>154</v>
       </c>
     </row>
-    <row r="143" spans="1:24">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B143">
         <v>2</v>
@@ -4291,9 +4313,9 @@
         <v>796</v>
       </c>
     </row>
-    <row r="144" spans="1:24">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B144">
         <v>3</v>
@@ -4317,9 +4339,9 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="145" spans="1:24">
+    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B145">
         <v>4</v>
@@ -4343,9 +4365,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="146" spans="1:24">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B146">
         <v>5</v>
@@ -4369,9 +4391,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="147" spans="1:24">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -4395,9 +4417,9 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="148" spans="1:24">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B148">
         <v>2</v>
@@ -4421,9 +4443,9 @@
         <v>337</v>
       </c>
     </row>
-    <row r="149" spans="1:24">
+    <row r="149" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B149">
         <v>3</v>
@@ -4447,9 +4469,9 @@
         <v>629</v>
       </c>
     </row>
-    <row r="150" spans="1:24">
+    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B150">
         <v>4</v>
@@ -4473,9 +4495,9 @@
         <v>117</v>
       </c>
     </row>
-    <row r="151" spans="1:24">
+    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B151">
         <v>5</v>
@@ -4499,9 +4521,9 @@
         <v>496</v>
       </c>
     </row>
-    <row r="152" spans="1:24">
+    <row r="152" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -4525,9 +4547,9 @@
         <v>524</v>
       </c>
     </row>
-    <row r="153" spans="1:24">
+    <row r="153" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B153">
         <v>2</v>
@@ -4551,9 +4573,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="154" spans="1:24">
+    <row r="154" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B154">
         <v>3</v>
@@ -4577,9 +4599,9 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="155" spans="1:24">
+    <row r="155" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B155">
         <v>4</v>
@@ -4603,9 +4625,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="156" spans="1:24">
+    <row r="156" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B156">
         <v>5</v>
@@ -4629,9 +4651,9 @@
         <v>111</v>
       </c>
     </row>
-    <row r="157" spans="1:24">
+    <row r="157" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -4655,9 +4677,9 @@
         <v>326</v>
       </c>
     </row>
-    <row r="158" spans="1:24">
+    <row r="158" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B158">
         <v>2</v>
@@ -4681,9 +4703,9 @@
         <v>236</v>
       </c>
     </row>
-    <row r="159" spans="1:24">
+    <row r="159" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B159">
         <v>3</v>
@@ -4707,9 +4729,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="160" spans="1:24">
+    <row r="160" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B160">
         <v>4</v>
@@ -4733,9 +4755,9 @@
         <v>399</v>
       </c>
     </row>
-    <row r="161" spans="1:24">
+    <row r="161" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B161">
         <v>5</v>
@@ -4759,9 +4781,9 @@
         <v>265</v>
       </c>
     </row>
-    <row r="162" spans="1:24">
+    <row r="162" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -4785,9 +4807,9 @@
         <v>627</v>
       </c>
     </row>
-    <row r="163" spans="1:24">
+    <row r="163" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B163">
         <v>2</v>
@@ -4811,9 +4833,9 @@
         <v>277</v>
       </c>
     </row>
-    <row r="164" spans="1:24">
+    <row r="164" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B164">
         <v>3</v>
@@ -4837,9 +4859,9 @@
         <v>399</v>
       </c>
     </row>
-    <row r="165" spans="1:24">
+    <row r="165" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B165">
         <v>4</v>
@@ -4863,9 +4885,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="166" spans="1:24">
+    <row r="166" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B166">
         <v>5</v>
@@ -4889,9 +4911,9 @@
         <v>399</v>
       </c>
     </row>
-    <row r="167" spans="1:24">
+    <row r="167" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -4915,9 +4937,9 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="168" spans="1:24">
+    <row r="168" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B168">
         <v>2</v>
@@ -4941,9 +4963,9 @@
         <v>157</v>
       </c>
     </row>
-    <row r="169" spans="1:24">
+    <row r="169" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B169">
         <v>3</v>
@@ -4967,9 +4989,9 @@
         <v>397</v>
       </c>
     </row>
-    <row r="170" spans="1:24">
+    <row r="170" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B170">
         <v>4</v>
@@ -4993,9 +5015,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="171" spans="1:24">
+    <row r="171" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B171">
         <v>5</v>
@@ -5019,9 +5041,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="172" spans="1:24">
+    <row r="172" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -5045,9 +5067,9 @@
         <v>503</v>
       </c>
     </row>
-    <row r="173" spans="1:24">
+    <row r="173" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B173">
         <v>2</v>
@@ -5071,9 +5093,9 @@
         <v>995</v>
       </c>
     </row>
-    <row r="174" spans="1:24">
+    <row r="174" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B174">
         <v>3</v>
@@ -5097,9 +5119,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:24">
+    <row r="175" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B175">
         <v>4</v>
@@ -5123,9 +5145,9 @@
         <v>296</v>
       </c>
     </row>
-    <row r="176" spans="1:24">
+    <row r="176" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B176">
         <v>5</v>
